--- a/docs/data/balance-rules.xlsx
+++ b/docs/data/balance-rules.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Reb7ec769de3f4204"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRules" sheetId="2" r:id="R257a3fc6ed934b4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R9ebb5a034d9a4bb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRules" sheetId="2" r:id="R0f93057243674349"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -148,7 +148,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="24">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -191,6 +191,27 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -435,7 +456,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>本工作簿是设计规则参考，不导出运行时 JSON。</x:v>
+        <x:v>学习与战斗基础逻辑受 docs/design_invariants.md 保护；这里只允许直接调整数值与公式。</x:v>
       </x:c>
       <x:c r="B3" s="12"/>
       <x:c r="C3" s="12"/>
@@ -455,7 +476,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>运行时实现仍以 Godot 场景与 GDScript 为唯一事实来源。</x:v>
+        <x:v>结构修改须先列明影响，并取得用户后续一次性明确确认。</x:v>
       </x:c>
       <x:c r="B5" s="12"/>
       <x:c r="C5" s="12"/>
@@ -494,572 +515,740 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:cols>
-    <x:col min="1" max="1" width="16.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="40" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="40" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="70" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="60" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="17" t="str">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="24" t="str">
         <x:v>category</x:v>
       </x:c>
-      <x:c r="B1" s="18" t="str">
+      <x:c r="B1" s="25" t="str">
         <x:v>key</x:v>
       </x:c>
-      <x:c r="C1" s="18" t="str">
+      <x:c r="C1" s="25" t="str">
         <x:v>value</x:v>
       </x:c>
-      <x:c r="D1" s="18" t="str">
+      <x:c r="D1" s="25" t="str">
         <x:v>formula</x:v>
       </x:c>
-      <x:c r="E1" s="19" t="str">
+      <x:c r="E1" s="26" t="str">
         <x:v>notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="21" t="str">
+    <x:row r="2" ht="24" hidden="0" customHeight="1">
+      <x:c r="A2" s="27" t="str">
+        <x:v>不变量</x:v>
+      </x:c>
+      <x:c r="B2" s="27" t="str">
+        <x:v>学习资源与阶段</x:v>
+      </x:c>
+      <x:c r="C2" s="27" t="str">
+        <x:v>潜能→灵感转换→固定学习经验满→按实际潜能支付Token→升级</x:v>
+      </x:c>
+      <x:c r="D2" s="27" t="str">
+        <x:v>数值与公式可调；资源身份和阶段顺序不可擅改</x:v>
+      </x:c>
+      <x:c r="E2" s="27" t="str">
+        <x:v>固定经验不读取灵感且每级增长；结构修改需用户后续明确确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" hidden="0" customHeight="1">
+      <x:c r="A3" s="28" t="str">
+        <x:v>不变量</x:v>
+      </x:c>
+      <x:c r="B3" s="28" t="str">
+        <x:v>战斗输入与职责</x:v>
+      </x:c>
+      <x:c r="C3" s="28" t="str">
+        <x:v>四属性+已装备功法+装备+状态/伤势/精力/加力/主动招式</x:v>
+      </x:c>
+      <x:c r="D3" s="28" t="str">
+        <x:v>玩家与NPC同口径聚合，combatRank仅缩放NPC体力与普通奖励</x:v>
+      </x:c>
+      <x:c r="E3" s="28" t="str">
+        <x:v>不得删除输入、交换四属性职责、让未装备功法生效或加入隐藏倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="28" t="str">
+        <x:v>治理</x:v>
+      </x:c>
+      <x:c r="B4" s="28" t="str">
+        <x:v>修改授权边界</x:v>
+      </x:c>
+      <x:c r="C4" s="28" t="str">
+        <x:v>数值、系数、阈值和计算公式可调</x:v>
+      </x:c>
+      <x:c r="D4" s="28" t="str">
+        <x:v>结构修改先列出文件/行为/存档数据/测试影响，再等待一次性确认</x:v>
+      </x:c>
+      <x:c r="E4" s="28" t="str">
+        <x:v>首次提出不视为授权；测试通过不能替代用户确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" hidden="0" customHeight="1">
+      <x:c r="A5" s="28" t="str">
         <x:v>目标</x:v>
       </x:c>
-      <x:c r="B2" s="21" t="str">
+      <x:c r="B5" s="28" t="str">
         <x:v>非战斗单位</x:v>
       </x:c>
-      <x:c r="C2" s="21" t="str">
-        <x:v>均衡新手1次有效命中、攻击尝试P90≤2；极端低编码中位4/P90 6次攻击尝试</x:v>
-      </x:c>
-      <x:c r="D2" s="21" t="str"/>
-      <x:c r="E2" s="21" t="str">
-        <x:v>儿童、商贩等不靠堆血延长战斗</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="22" t="str">
+      <x:c r="C5" s="28" t="str">
+        <x:v>均衡新手中位2–4/P90≤5；低编码合法新手中位6–9/P90≤12次攻击尝试</x:v>
+      </x:c>
+      <x:c r="D5" s="28" t="str"/>
+      <x:c r="E5" s="28" t="str">
+        <x:v>小学生固定100体力，不再被普通攻击一击击倒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="28" t="str">
         <x:v>目标</x:v>
       </x:c>
-      <x:c r="B3" s="22" t="str">
+      <x:c r="B6" s="28" t="str">
         <x:v>同属性同功法镜像战</x:v>
       </x:c>
-      <x:c r="C3" s="22" t="str">
+      <x:c r="C6" s="28" t="str">
         <x:v>8–12 回合</x:v>
       </x:c>
-      <x:c r="D3" s="22" t="str">
+      <x:c r="D6" s="28" t="str">
         <x:v>双方同四维、同功法；无闪避/装备/道具/加力/主动招式；每回合至多各命中一次普攻</x:v>
       </x:c>
-      <x:c r="E3" s="22" t="str">
+      <x:c r="E6" s="28" t="str">
         <x:v>保留暴击、完整功法被动招架、减伤和±10%伤害浮动</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="22" t="str">
+    <x:row r="7" ht="24" hidden="0" customHeight="1">
+      <x:c r="A7" s="28" t="str">
         <x:v>校准</x:v>
       </x:c>
-      <x:c r="B4" s="22" t="str">
+      <x:c r="B7" s="28" t="str">
         <x:v>四门派镜像 P10/中位/P90</x:v>
       </x:c>
-      <x:c r="C4" s="22" t="str">
+      <x:c r="C7" s="28" t="str">
         <x:v>L0 8/8/9；L20 8–9/9/10；L60 8–9/9–10/10–11；L100 8–9/9–10/10–11</x:v>
       </x:c>
-      <x:c r="D4" s="22" t="str">
+      <x:c r="D7" s="28" t="str">
         <x:v>NG / React / Vue / Vanilla，各等级10,000次随机模拟</x:v>
       </x:c>
-      <x:c r="E4" s="22" t="str">
+      <x:c r="E7" s="28" t="str">
         <x:v>16组P10、中位与P90全部位于8–12回合</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="22" t="str">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="28" t="str">
         <x:v>目标</x:v>
       </x:c>
-      <x:c r="B5" s="22" t="str">
+      <x:c r="B8" s="28" t="str">
         <x:v>精英 / Boss</x:v>
       </x:c>
-      <x:c r="C5" s="22" t="str">
+      <x:c r="C8" s="28" t="str">
         <x:v>8–12 / 10–14 个决策</x:v>
       </x:c>
-      <x:c r="D5" s="22" t="str"/>
-      <x:c r="E5" s="22" t="str">
+      <x:c r="D8" s="28" t="str"/>
+      <x:c r="E8" s="28" t="str">
         <x:v>通过技能与阶段而非无限回血延长</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="22" t="str">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="28" t="str">
         <x:v>基础</x:v>
       </x:c>
-      <x:c r="B6" s="22" t="str">
+      <x:c r="B9" s="28" t="str">
         <x:v>攻击</x:v>
       </x:c>
-      <x:c r="C6" s="22" t="str"/>
-      <x:c r="D6" s="22" t="str">
-        <x:v>floor(10 + 编码×1.8×centeredScale(编码,0.004,0.90,1.10))</x:v>
-      </x:c>
-      <x:c r="E6" s="22" t="str">
-        <x:v>再加功法与装备攻击</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="22" t="str">
+      <x:c r="C9" s="28" t="str"/>
+      <x:c r="D9" s="28" t="str">
+        <x:v>12 + 编码×1.50×centeredScale(编码,0.003,0.94,1.08)</x:v>
+      </x:c>
+      <x:c r="E9" s="28" t="str">
+        <x:v>最少为1，再加功法与装备攻击</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="28" t="str">
         <x:v>基础</x:v>
       </x:c>
-      <x:c r="B7" s="22" t="str">
+      <x:c r="B10" s="28" t="str">
         <x:v>防御</x:v>
       </x:c>
-      <x:c r="C7" s="22" t="str"/>
-      <x:c r="D7" s="22" t="str">
-        <x:v>floor(架构×1.2×centeredScale(架构,0.003,0.92,1.08))</x:v>
-      </x:c>
-      <x:c r="E7" s="22" t="str">
-        <x:v>再加功法与装备防御</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="22" t="str">
+      <x:c r="C10" s="28" t="str"/>
+      <x:c r="D10" s="28" t="str">
+        <x:v>架构×0.95×centeredScale(架构,0.0025,0.94,1.07)</x:v>
+      </x:c>
+      <x:c r="E10" s="28" t="str">
+        <x:v>最少为0，再加功法与装备防御</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="28" t="str">
         <x:v>资源</x:v>
       </x:c>
-      <x:c r="B8" s="22" t="str">
+      <x:c r="B11" s="28" t="str">
         <x:v>体力上限</x:v>
       </x:c>
-      <x:c r="C8" s="22" t="str"/>
-      <x:c r="D8" s="22" t="str">
-        <x:v>186 + 架构×6 + floor(sqrt(精力上限)×3)</x:v>
-      </x:c>
-      <x:c r="E8" s="22" t="str">
+      <x:c r="C11" s="28" t="str"/>
+      <x:c r="D11" s="28" t="str">
+        <x:v>floor(190 + 架构×5.2) + floor(sqrt(精力上限)×3)</x:v>
+      </x:c>
+      <x:c r="E11" s="28" t="str">
         <x:v>以生命池承载8–12回合基准；精力仍只按平方根反哺体力</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="22" t="str">
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="28" t="str">
         <x:v>资源</x:v>
       </x:c>
-      <x:c r="B9" s="22" t="str">
+      <x:c r="B12" s="28" t="str">
+        <x:v>食物/饮水容量</x:v>
+      </x:c>
+      <x:c r="C12" s="28" t="str"/>
+      <x:c r="D12" s="28" t="str">
+        <x:v>200 + 编码×6</x:v>
+      </x:c>
+      <x:c r="E12" s="28" t="str">
+        <x:v>创建角色、读档归一化、物品和世界事件共用唯一公式</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="28" t="str">
+        <x:v>资源</x:v>
+      </x:c>
+      <x:c r="B13" s="28" t="str">
         <x:v>玩家精力上限</x:v>
       </x:c>
-      <x:c r="C9" s="22" t="str"/>
-      <x:c r="D9" s="22" t="str">
+      <x:c r="C13" s="28" t="str"/>
+      <x:c r="D13" s="28" t="str">
         <x:v>精力修为 + 装备功法 mpMaxPerLv 加成</x:v>
       </x:c>
-      <x:c r="E9" s="22" t="str">
+      <x:c r="E13" s="28" t="str">
         <x:v>功法上限字段已接入运行时</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="22" t="str">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="28" t="str">
         <x:v>资源</x:v>
       </x:c>
-      <x:c r="B10" s="22" t="str">
+      <x:c r="B14" s="28" t="str">
         <x:v>NPC精力上限</x:v>
       </x:c>
-      <x:c r="C10" s="22" t="str"/>
-      <x:c r="D10" s="22" t="str">
+      <x:c r="C14" s="28" t="str"/>
+      <x:c r="D14" s="28" t="str">
         <x:v>floor(内功值×25×架构修正) + 装备功法 mpMaxPerLv 加成</x:v>
       </x:c>
-      <x:c r="E10" s="22" t="str">
+      <x:c r="E14" s="28" t="str">
         <x:v>NPC 内功值来自基础架构与已装备门派架构功法</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="22" t="str">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="28" t="str">
         <x:v>判定</x:v>
       </x:c>
-      <x:c r="B11" s="22" t="str">
+      <x:c r="B15" s="28" t="str">
         <x:v>命中率</x:v>
       </x:c>
-      <x:c r="C11" s="22" t="str">
+      <x:c r="C15" s="28" t="str">
         <x:v>45%–95%</x:v>
       </x:c>
-      <x:c r="D11" s="22" t="str">
-        <x:v>clamp(78% + (攻方思维-守方思维)×1.2% + 命中加成 - 闪避加成)</x:v>
-      </x:c>
-      <x:c r="E11" s="22" t="str">
+      <x:c r="D15" s="28" t="str">
+        <x:v>clamp(78% + (攻方思维-守方思维)×0.9% + 命中加成 - 闪避加成)</x:v>
+      </x:c>
+      <x:c r="E15" s="28" t="str">
         <x:v>减少连续空回合</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="22" t="str">
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="28" t="str">
         <x:v>判定</x:v>
       </x:c>
-      <x:c r="B12" s="22" t="str">
+      <x:c r="B16" s="28" t="str">
         <x:v>减伤率</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="str"/>
-      <x:c r="D12" s="22" t="str">
+      <x:c r="C16" s="28" t="str"/>
+      <x:c r="D16" s="28" t="str">
         <x:v>防御/(防御+100)</x:v>
       </x:c>
-      <x:c r="E12" s="22" t="str">
+      <x:c r="E16" s="28" t="str">
         <x:v>递减收益</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="22" t="str">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="28" t="str">
         <x:v>判定</x:v>
       </x:c>
-      <x:c r="B13" s="22" t="str">
+      <x:c r="B17" s="28" t="str">
         <x:v>招架率</x:v>
       </x:c>
-      <x:c r="C13" s="22" t="str">
+      <x:c r="C17" s="28" t="str">
         <x:v>0%–55%</x:v>
       </x:c>
-      <x:c r="D13" s="22" t="str">
-        <x:v>clamp(4% + 编码×0.4% + 功法/装备招架)</x:v>
-      </x:c>
-      <x:c r="E13" s="22" t="str">
+      <x:c r="D17" s="28" t="str">
+        <x:v>clamp(4% + 编码×0.25% + 功法/装备招架)</x:v>
+      </x:c>
+      <x:c r="E17" s="28" t="str">
         <x:v>招架后保留 60% 伤害</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="22" t="str">
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="28" t="str">
         <x:v>判定</x:v>
       </x:c>
-      <x:c r="B14" s="22" t="str">
+      <x:c r="B18" s="28" t="str">
         <x:v>暴击率</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="str">
+      <x:c r="C18" s="28" t="str">
         <x:v>2%–30%</x:v>
       </x:c>
-      <x:c r="D14" s="22" t="str">
-        <x:v>clamp(3% + 思维×0.15% + 灵感×0.15% + 装备暴击)</x:v>
-      </x:c>
-      <x:c r="E14" s="22" t="str">
-        <x:v>架构不再负责暴击</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="22" t="str">
+      <x:c r="D18" s="28" t="str">
+        <x:v>clamp(3% + 灵感×0.30% + 装备暴击)</x:v>
+      </x:c>
+      <x:c r="E18" s="28" t="str">
+        <x:v>暴击属性集中到灵感</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="28" t="str">
         <x:v>技能</x:v>
       </x:c>
-      <x:c r="B15" s="22" t="str">
+      <x:c r="B19" s="28" t="str">
         <x:v>招式触发</x:v>
       </x:c>
-      <x:c r="C15" s="22" t="str">
+      <x:c r="C19" s="28" t="str">
         <x:v>攻击≤45%；闪避≤27%；招架≤35%</x:v>
       </x:c>
-      <x:c r="D15" s="22" t="str">
+      <x:c r="D19" s="28" t="str">
         <x:v>各类型使用独立 base + count×perMove</x:v>
       </x:c>
-      <x:c r="E15" s="22" t="str">
+      <x:c r="E19" s="28" t="str">
         <x:v>避免多层完全回避锁死战斗</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="22" t="str">
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="28" t="str">
         <x:v>技能</x:v>
       </x:c>
-      <x:c r="B16" s="22" t="str">
+      <x:c r="B20" s="28" t="str">
         <x:v>加力</x:v>
       </x:c>
-      <x:c r="C16" s="22" t="str">
+      <x:c r="C20" s="28" t="str">
         <x:v>额外伤害≤75%</x:v>
       </x:c>
-      <x:c r="D16" s="22" t="str">
+      <x:c r="D20" s="28" t="str">
         <x:v>伤害×min(75%, 加力/(加力+100))×随机0.9–1.1</x:v>
       </x:c>
-      <x:c r="E16" s="22" t="str">
+      <x:c r="E20" s="28" t="str">
         <x:v>递减收益，不再直接平铺数百点</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="22" t="str">
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="28" t="str">
         <x:v>AI</x:v>
       </x:c>
-      <x:c r="B17" s="22" t="str">
+      <x:c r="B21" s="28" t="str">
         <x:v>NPC 加力</x:v>
       </x:c>
-      <x:c r="C17" s="22" t="str">
+      <x:c r="C21" s="28" t="str">
         <x:v>默认 45% 概率、25% 内功</x:v>
       </x:c>
-      <x:c r="D17" s="22" t="str">
+      <x:c r="D21" s="28" t="str">
         <x:v>可由 ai.forceUseRate / forceRatio 覆盖</x:v>
       </x:c>
-      <x:c r="E17" s="22" t="str">
+      <x:c r="E21" s="28" t="str">
         <x:v>高阶人物有爆发但不再每击全力</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="22" t="str">
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="28" t="str">
         <x:v>AI</x:v>
       </x:c>
-      <x:c r="B18" s="22" t="str">
+      <x:c r="B22" s="28" t="str">
         <x:v>NPC 摸鱼</x:v>
       </x:c>
-      <x:c r="C18" s="22" t="str">
+      <x:c r="C22" s="28" t="str">
         <x:v>默认每战 1 次，最多回 18%</x:v>
       </x:c>
-      <x:c r="D18" s="22" t="str">
+      <x:c r="D22" s="28" t="str">
         <x:v>体力低于35%且精力足够时20%概率</x:v>
       </x:c>
-      <x:c r="E18" s="22" t="str">
+      <x:c r="E22" s="28" t="str">
         <x:v>不会反复重置血条</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="22" t="str">
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="28" t="str">
         <x:v>恢复</x:v>
       </x:c>
-      <x:c r="B19" s="22" t="str">
+      <x:c r="B23" s="28" t="str">
         <x:v>玩家摸鱼 / 用药</x:v>
       </x:c>
-      <x:c r="C19" s="22" t="str">
+      <x:c r="C23" s="28" t="str">
         <x:v>每战 1 次 / 2 次</x:v>
       </x:c>
-      <x:c r="D19" s="22" t="str">
+      <x:c r="D23" s="28" t="str">
         <x:v>摸鱼最多恢复20%最大体力</x:v>
       </x:c>
-      <x:c r="E19" s="22" t="str">
+      <x:c r="E23" s="28" t="str">
         <x:v>受保护 HUD 未改，以次数上限约束免费动作</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="22" t="str">
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="28" t="str">
         <x:v>伤势</x:v>
       </x:c>
-      <x:c r="B20" s="22" t="str">
+      <x:c r="B24" s="28" t="str">
         <x:v>战后伤势</x:v>
       </x:c>
-      <x:c r="C20" s="22" t="str">
+      <x:c r="C24" s="28" t="str">
         <x:v>单场≤真实体力20%</x:v>
       </x:c>
-      <x:c r="D20" s="22" t="str">
+      <x:c r="D24" s="28" t="str">
         <x:v>净体力损失×15%×(1-功法伤势减免) + 当场重伤</x:v>
       </x:c>
-      <x:c r="E20" s="22" t="str">
+      <x:c r="E24" s="28" t="str">
         <x:v>不按累计受击重复惩罚治疗</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="22" t="str">
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="28" t="str">
         <x:v>伤势</x:v>
       </x:c>
-      <x:c r="B21" s="22" t="str">
+      <x:c r="B25" s="28" t="str">
         <x:v>破相判定</x:v>
       </x:c>
-      <x:c r="C21" s="22" t="str">
+      <x:c r="C25" s="28" t="str">
         <x:v>濒死15%；归零30%；每次容貌−20</x:v>
       </x:c>
-      <x:c r="D21" s="22" t="str">
+      <x:c r="D25" s="28" t="str">
         <x:v>两项独立判定且可叠加，仅致命战斗触发</x:v>
       </x:c>
-      <x:c r="E21" s="22" t="str">
+      <x:c r="E25" s="28" t="str">
         <x:v>容貌永久损失会写入角色状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="22" t="str">
+    <x:row r="26" ht="24" hidden="0" customHeight="1">
+      <x:c r="A26" s="28" t="str">
         <x:v>战败</x:v>
       </x:c>
-      <x:c r="B22" s="22" t="str">
+      <x:c r="B26" s="28" t="str">
         <x:v>资源与功法惩罚</x:v>
       </x:c>
-      <x:c r="C22" s="22" t="str">
+      <x:c r="C26" s="28" t="str">
         <x:v>经验/潜能/Token各−5%～10%；25%概率最多一门功法−1级</x:v>
       </x:c>
-      <x:c r="D22" s="22" t="str">
+      <x:c r="D26" s="28" t="str">
         <x:v>三类资源分别随机5%～10%；仅从高于保底等级的已学功法中随机一门</x:v>
       </x:c>
-      <x:c r="E22" s="22" t="str">
+      <x:c r="E26" s="28" t="str">
         <x:v>结算后立即重算派生属性与体力/精力上限</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="22" t="str">
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="28" t="str">
         <x:v>成长</x:v>
       </x:c>
-      <x:c r="B23" s="22" t="str">
-        <x:v>学习需求</x:v>
-      </x:c>
-      <x:c r="C23" s="22" t="str">
-        <x:v>满级单级跨度4</x:v>
-      </x:c>
-      <x:c r="D23" s="22" t="str">
-        <x:v>二次曲线，灵感倍率65%–125%，结果向上取偶数</x:v>
-      </x:c>
-      <x:c r="E23" s="22" t="str">
-        <x:v>旧跨度20下调，减少重复任务量</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="22" t="str">
+      <x:c r="B27" s="28" t="str">
+        <x:v>固定学习经验</x:v>
+      </x:c>
+      <x:c r="C27" s="28" t="str">
+        <x:v>基础Lv1需60；每级至少+20</x:v>
+      </x:c>
+      <x:c r="D27" s="28" t="str">
+        <x:v>10×max(2.25次等级曲线,(5+目标等级)×costFactor,前一级经验单位+2)</x:v>
+      </x:c>
+      <x:c r="E27" s="28" t="str">
+        <x:v>与灵感完全无关；基础前10级为60/80/100/120/140/160/180/200/220/240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="28" t="str">
+        <x:v>成长</x:v>
+      </x:c>
+      <x:c r="B28" s="28" t="str">
+        <x:v>潜能转化学习经验</x:v>
+      </x:c>
+      <x:c r="C28" s="28" t="str">
+        <x:v>灵感0/25/50：每潜能8/10/14经验</x:v>
+      </x:c>
+      <x:c r="D28" s="28" t="str">
+        <x:v>round(10 / clamp(1-(灵感-25)×1.5%,70%,130%))</x:v>
+      </x:c>
+      <x:c r="E28" s="28" t="str">
+        <x:v>每个时间片消耗1潜能；灵感越高，升级越快且潜能越省</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="28" t="str">
+        <x:v>成长</x:v>
+      </x:c>
+      <x:c r="B29" s="28" t="str">
+        <x:v>师父学习学费</x:v>
+      </x:c>
+      <x:c r="C29" s="28" t="str">
+        <x:v>本级实际潜能消耗的65%</x:v>
+      </x:c>
+      <x:c r="D29" s="28" t="str">
+        <x:v>ceil(本级累计潜能消耗×0.65)</x:v>
+      </x:c>
+      <x:c r="E29" s="28" t="str">
+        <x:v>固定经验满后支付；高灵感因潜能消耗更少而同步节省Token</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="28" t="str">
+        <x:v>成长</x:v>
+      </x:c>
+      <x:c r="B30" s="28" t="str">
+        <x:v>标准100级路线</x:v>
+      </x:c>
+      <x:c r="C30" s="28" t="str">
+        <x:v>898,040经验 / 89,804潜能 / 58,646 Token</x:v>
+      </x:c>
+      <x:c r="D30" s="28" t="str">
+        <x:v>五门基础功法加一门本派架构功法，灵感25</x:v>
+      </x:c>
+      <x:c r="E30" s="28" t="str">
+        <x:v>约79.3小时；灵感50为64,401潜能/42,091 Token/约56.9小时</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="28" t="str">
         <x:v>任务</x:v>
       </x:c>
-      <x:c r="B24" s="22" t="str">
+      <x:c r="B31" s="28" t="str">
         <x:v>环任务成长</x:v>
       </x:c>
-      <x:c r="C24" s="22" t="str">
+      <x:c r="C31" s="28" t="str">
         <x:v>线性且封顶</x:v>
       </x:c>
-      <x:c r="D24" s="22" t="str">
+      <x:c r="D31" s="28" t="str">
         <x:v>1 + ringGrowth×(环数-1)，再受 growthCap 限制</x:v>
       </x:c>
-      <x:c r="E24" s="22" t="str">
+      <x:c r="E31" s="28" t="str">
         <x:v>悬赏奖励也改为基于初始值线性成长</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="22" t="str">
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="28" t="str">
         <x:v>任务</x:v>
       </x:c>
-      <x:c r="B25" s="22" t="str">
+      <x:c r="B32" s="28" t="str">
         <x:v>奖励互斥</x:v>
       </x:c>
-      <x:c r="C25" s="22" t="str">
+      <x:c r="C32" s="28" t="str">
         <x:v>任务奖励或野战奖励二选一</x:v>
       </x:c>
-      <x:c r="D25" s="22" t="str">
+      <x:c r="D32" s="28" t="str">
         <x:v>普通悬赏击杀先标记完成，回程交付时才发奖</x:v>
       </x:c>
-      <x:c r="E25" s="22" t="str">
+      <x:c r="E32" s="28" t="str">
         <x:v>防止同一目标重复获得两份奖励</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="22" t="str">
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="28" t="str">
         <x:v>任务</x:v>
       </x:c>
-      <x:c r="B26" s="22" t="str">
+      <x:c r="B33" s="28" t="str">
         <x:v>交付物退款</x:v>
       </x:c>
-      <x:c r="C26" s="22" t="str">
+      <x:c r="C33" s="28" t="str">
         <x:v>固定成本补偿</x:v>
       </x:c>
-      <x:c r="D26" s="22" t="str">
+      <x:c r="D33" s="28" t="str">
         <x:v>物品价格×itemRefundRate</x:v>
       </x:c>
-      <x:c r="E26" s="22" t="str">
+      <x:c r="E33" s="28" t="str">
         <x:v>退款不参与环数成长或随机浮动，服务费才属于奖励</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="22" t="str">
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="29" t="str">
         <x:v>任务</x:v>
       </x:c>
-      <x:c r="B27" s="22" t="str">
+      <x:c r="B34" s="29" t="str">
+        <x:v>导师新手项目</x:v>
+      </x:c>
+      <x:c r="C34" s="29" t="str">
+        <x:v>50经验 / 50潜能 / 40 Token</x:v>
+      </x:c>
+      <x:c r="D34" s="29" t="str">
+        <x:v>三个项目奖励固定，仅体力消耗分别为25/50/100</x:v>
+      </x:c>
+      <x:c r="E34" s="29" t="str">
+        <x:v>项目难度不再放大奖励</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" s="30" t="str">
+        <x:v>任务</x:v>
+      </x:c>
+      <x:c r="B35" s="30" t="str">
         <x:v>并行任务状态</x:v>
       </x:c>
-      <x:c r="C27" s="22" t="str">
+      <x:c r="C35" s="30" t="str">
         <x:v>不同任务可同时活动</x:v>
       </x:c>
-      <x:c r="D27" s="22" t="str">
+      <x:c r="D35" s="30" t="str">
         <x:v>固定任务按 quest_id；生成任务按 generator:&lt;generator_id&gt; 唯一</x:v>
       </x:c>
-      <x:c r="E27" s="22" t="str">
+      <x:c r="E35" s="30" t="str">
         <x:v>同一 runtime_id/生成器不可重复；任务仅存本局内存，重开或读档时清空</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="22" t="str">
+    <x:row r="36" ht="28.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A36" s="30" t="str">
         <x:v>任务</x:v>
       </x:c>
-      <x:c r="B28" s="22" t="str">
+      <x:c r="B36" s="30" t="str">
         <x:v>随机目标过滤</x:v>
       </x:c>
-      <x:c r="C28" s="22" t="str">
+      <x:c r="C36" s="30" t="str">
         <x:v>保护任务端点、非战斗与剧情人物</x:v>
       </x:c>
-      <x:c r="D28" s="22" t="str">
+      <x:c r="D36" s="30" t="str">
         <x:v>排除全部任务发布/交付端点、当前目标；击杀池另排除未满18岁、noncombatant、商贩、典当商、师父、显式保护人物</x:v>
       </x:c>
-      <x:c r="E28" s="22" t="str">
+      <x:c r="E36" s="30" t="str">
         <x:v>只有悬赏/击杀环响应击败事件，跑腿与谈话任务必须交付</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="22" t="str">
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" s="30" t="str">
         <x:v>人物</x:v>
       </x:c>
-      <x:c r="B29" s="22" t="str">
+      <x:c r="B37" s="30" t="str">
         <x:v>combatRank</x:v>
       </x:c>
-      <x:c r="C29" s="22" t="str">
+      <x:c r="C37" s="30" t="str">
         <x:v>noncombatant→legendary 共7档</x:v>
       </x:c>
-      <x:c r="D29" s="22" t="str">
+      <x:c r="D37" s="30" t="str">
         <x:v>仅缩放生命池与普通奖励</x:v>
       </x:c>
-      <x:c r="E29" s="22" t="str">
+      <x:c r="E37" s="30" t="str">
         <x:v>攻击、防御仍来自显式四维、功法、装备</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="22" t="str">
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
+      <x:c r="A38" s="30" t="str">
         <x:v>人物</x:v>
       </x:c>
-      <x:c r="B30" s="22" t="str">
+      <x:c r="B38" s="30" t="str">
         <x:v>combatRank 生命倍率</x:v>
       </x:c>
-      <x:c r="C30" s="22" t="str">
-        <x:v>0.24 / 0.78 / 0.92 / 1.00 / 1.10 / 1.20 / 1.30</x:v>
-      </x:c>
-      <x:c r="D30" s="22" t="str">
+      <x:c r="C38" s="30" t="str">
+        <x:v>0.50 / 0.78 / 0.92 / 1.00 / 1.10 / 1.20 / 1.30</x:v>
+      </x:c>
+      <x:c r="D38" s="30" t="str">
         <x:v>noncombatant / novice / trained / veteran / elite / master / legendary</x:v>
       </x:c>
-      <x:c r="E30" s="22" t="str">
-        <x:v>小学生为 noncombatant：2架构、0精力时最终48体力</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="22" t="str">
+      <x:c r="E38" s="30" t="str">
+        <x:v>小学生为noncombatant：1.8架构、0精力时最终100体力</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
+      <x:c r="A39" s="30" t="str">
         <x:v>人物</x:v>
       </x:c>
-      <x:c r="B31" s="22" t="str">
+      <x:c r="B39" s="30" t="str">
         <x:v>combatRank 奖励倍率</x:v>
       </x:c>
-      <x:c r="C31" s="22" t="str">
+      <x:c r="C39" s="30" t="str">
         <x:v>0.15 / 0.50 / 0.75 / 1.00 / 1.20 / 1.50 / 2.00</x:v>
       </x:c>
-      <x:c r="D31" s="22" t="str">
+      <x:c r="D39" s="30" t="str">
         <x:v>noncombatant / novice / trained / veteran / elite / master / legendary</x:v>
       </x:c>
-      <x:c r="E31" s="22" t="str">
+      <x:c r="E39" s="30" t="str">
         <x:v>战斗奖励与生命倍率分离，非战斗人物不成为刷取目标</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="22" t="str">
+    <x:row r="40" ht="15" hidden="0" customHeight="1">
+      <x:c r="A40" s="30" t="str">
         <x:v>人物</x:v>
       </x:c>
-      <x:c r="B32" s="22" t="str">
+      <x:c r="B40" s="30" t="str">
         <x:v>combatRole</x:v>
       </x:c>
-      <x:c r="C32" s="22" t="str">
+      <x:c r="C40" s="30" t="str">
         <x:v>7种原型</x:v>
       </x:c>
-      <x:c r="D32" s="22" t="str">
+      <x:c r="D40" s="30" t="str">
         <x:v>noncombatant/striker/skirmisher/tank/counter/controller/balanced</x:v>
       </x:c>
-      <x:c r="E32" s="22" t="str">
+      <x:c r="E40" s="30" t="str">
         <x:v>66 人四维配点全部唯一且总点数不变</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="22" t="str">
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
+      <x:c r="A41" s="30" t="str">
         <x:v>状态</x:v>
       </x:c>
-      <x:c r="B33" s="22" t="str">
+      <x:c r="B41" s="30" t="str">
         <x:v>资源归一化</x:v>
       </x:c>
-      <x:c r="C33" s="22" t="str">
+      <x:c r="C41" s="30" t="str">
         <x:v>上限变化即时钳制</x:v>
       </x:c>
-      <x:c r="D33" s="22" t="str">
+      <x:c r="D41" s="30" t="str">
         <x:v>卸功法或战败降级后重算四维、体力与精力上限</x:v>
       </x:c>
-      <x:c r="E33" s="22" t="str">
+      <x:c r="E41" s="30" t="str">
         <x:v>不允许保存当前值高于新上限</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="23" t="str">
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
+      <x:c r="A42" s="30" t="str">
+        <x:v>界面</x:v>
+      </x:c>
+      <x:c r="B42" s="30" t="str">
+        <x:v>战斗大数值排版</x:v>
+      </x:c>
+      <x:c r="C42" s="30" t="str">
+        <x:v>体力与精力支持5–6位数</x:v>
+      </x:c>
+      <x:c r="D42" s="30" t="str">
+        <x:v>双方统计分列显示；伤势百分比独立位于体力条上方</x:v>
+      </x:c>
+      <x:c r="E42" s="30" t="str">
+        <x:v>数值、标签和进度条不得互相覆盖</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
+      <x:c r="A43" s="30" t="str">
+        <x:v>界面</x:v>
+      </x:c>
+      <x:c r="B43" s="30" t="str">
+        <x:v>顶部进度条宽度</x:v>
+      </x:c>
+      <x:c r="C43" s="30" t="str">
+        <x:v>从地图徽标后8px延伸至右边界前16px</x:v>
+      </x:c>
+      <x:c r="D43" s="30" t="str">
+        <x:v>left=mapBadge.right+8；right=viewportWidth-16</x:v>
+      </x:c>
+      <x:c r="E43" s="30" t="str">
+        <x:v>480逻辑视口下约316px，充分使用右侧空间</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
+      <x:c r="A44" s="30" t="str">
         <x:v>存档</x:v>
       </x:c>
-      <x:c r="B34" s="23" t="str">
+      <x:c r="B44" s="30" t="str">
         <x:v>v5 版本边界</x:v>
       </x:c>
-      <x:c r="C34" s="23" t="str">
+      <x:c r="C44" s="30" t="str">
         <x:v>仅接受当前版本</x:v>
       </x:c>
-      <x:c r="D34" s="23" t="str">
+      <x:c r="D44" s="30" t="str">
         <x:v>version == 5</x:v>
       </x:c>
-      <x:c r="E34" s="23" t="str">
+      <x:c r="E44" s="30" t="str">
         <x:v>资源主键已切换为 UUID；v2、v3、v4 存档全部作废且不迁移</x:v>
       </x:c>
     </x:row>

--- a/docs/data/balance-rules.xlsx
+++ b/docs/data/balance-rules.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R9ebb5a034d9a4bb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRules" sheetId="2" r:id="R0f93057243674349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R037e527f8efe4354"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRules" sheetId="2" r:id="R9324cf74bdf64481"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -47,13 +47,13 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="16"/>
+      <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
     </x:font>
     <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF243B53"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF38536B"/>
       <x:name val="Calibri"/>
     </x:font>
     <x:font>
@@ -72,83 +72,40 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF16324F"/>
+        <x:fgColor rgb="FF173A5E"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFEAF2F8"/>
+        <x:fgColor rgb="FFE7F0F7"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF217A8A"/>
+        <x:fgColor rgb="FF227F8C"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="3">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF165A66"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FF165A66"/>
-      </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FF165A66"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FF165A66"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF165A66"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF165A66"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:bottom style="thin">
-        <x:color rgb="FF9FB3C8"/>
+        <x:color rgb="FFD7E1E8"/>
       </x:bottom>
     </x:border>
     <x:border>
       <x:top style="thin">
-        <x:color rgb="FF165A66"/>
+        <x:color rgb="FFD7E1E8"/>
       </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FF165A66"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:bottom style="thin">
-        <x:color rgb="FFE6EDF3"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFE6EDF3"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFE6EDF3"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFE6EDF3"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFBCCCDC"/>
+        <x:color rgb="FFD7E1E8"/>
       </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -162,55 +119,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -431,82 +348,62 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:cols>
     <x:col min="1" max="1" width="28.889999389648438" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="57.779998779296875" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="84.44000244140625" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
+    <x:row r="1" ht="28.5" customHeight="1">
       <x:c r="A1" s="3" t="str">
         <x:v>FrontendLegends · 平衡规则</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-      <x:c r="D1" s="3"/>
-      <x:c r="E1" s="3"/>
-      <x:c r="F1" s="3"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="12" t="str">
+    </x:row>
+    <x:row r="2" ht="18" customHeight="1">
+      <x:c r="A2" s="6" t="str">
         <x:v>本工作簿独立记录平衡规则；运行时实现仍以 Godot 场景与 GDScript 为准。</x:v>
       </x:c>
-      <x:c r="B2" s="12"/>
-      <x:c r="C2" s="12"/>
-      <x:c r="D2" s="12"/>
-      <x:c r="E2" s="12"/>
-      <x:c r="F2" s="12"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="12" t="str">
-        <x:v>学习与战斗基础逻辑受 docs/design_invariants.md 保护；这里只允许直接调整数值与公式。</x:v>
-      </x:c>
-      <x:c r="B3" s="12"/>
-      <x:c r="C3" s="12"/>
-      <x:c r="D3" s="12"/>
-      <x:c r="E3" s="12"/>
-      <x:c r="F3" s="12"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="12" t="str">
+      <x:c r="B2" s="6"/>
+    </x:row>
+    <x:row r="3" ht="18" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>本工作簿是设计规则参考，不导出运行时 JSON。</x:v>
+      </x:c>
+      <x:c r="B3" s="6"/>
+    </x:row>
+    <x:row r="4" ht="18" customHeight="1">
+      <x:c r="A4" s="6" t="str">
         <x:v>从代码中的规则清单重建：npm run data:excel -- --file=balance</x:v>
       </x:c>
-      <x:c r="B4" s="12"/>
-      <x:c r="C4" s="12"/>
-      <x:c r="D4" s="12"/>
-      <x:c r="E4" s="12"/>
-      <x:c r="F4" s="12"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="12" t="str">
-        <x:v>结构修改须先列明影响，并取得用户后续一次性明确确认。</x:v>
-      </x:c>
-      <x:c r="B5" s="12"/>
-      <x:c r="C5" s="12"/>
-      <x:c r="D5" s="12"/>
-      <x:c r="E5" s="12"/>
-      <x:c r="F5" s="12"/>
+      <x:c r="B4" s="6"/>
+    </x:row>
+    <x:row r="5" ht="18" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>运行时实现仍以 Godot 场景与 GDScript 为唯一事实来源。</x:v>
+      </x:c>
+      <x:c r="B5" s="6"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="9" t="str">
+      <x:c r="A7" s="8" t="str">
         <x:v>Sheet</x:v>
       </x:c>
-      <x:c r="B7" s="10" t="str">
+      <x:c r="B7" s="8" t="str">
         <x:v>用途</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11" t="str">
+      <x:c r="A8" t="str">
         <x:v>BalanceRules</x:v>
       </x:c>
-      <x:c r="B8" s="11" t="str">
+      <x:c r="B8" t="str">
         <x:v>数值目标、运行时公式与约束</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
-    <x:mergeCell ref="A2:F2"/>
-    <x:mergeCell ref="A3:F3"/>
-    <x:mergeCell ref="A4:F4"/>
-    <x:mergeCell ref="A5:F5"/>
+    <x:mergeCell ref="A1:B1"/>
+    <x:mergeCell ref="A2:B2"/>
+    <x:mergeCell ref="A3:B3"/>
+    <x:mergeCell ref="A4:B4"/>
+    <x:mergeCell ref="A5:B5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -515,740 +412,774 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12.220000267028809" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="27.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="37.779998779296875" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="70" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="60" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="24" t="str">
+    <x:row r="1" ht="18" customHeight="1">
+      <x:c r="A1" s="14" t="str">
         <x:v>category</x:v>
       </x:c>
-      <x:c r="B1" s="25" t="str">
+      <x:c r="B1" s="14" t="str">
         <x:v>key</x:v>
       </x:c>
-      <x:c r="C1" s="25" t="str">
+      <x:c r="C1" s="14" t="str">
         <x:v>value</x:v>
       </x:c>
-      <x:c r="D1" s="25" t="str">
+      <x:c r="D1" s="14" t="str">
         <x:v>formula</x:v>
       </x:c>
-      <x:c r="E1" s="26" t="str">
+      <x:c r="E1" s="14" t="str">
         <x:v>notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="24" hidden="0" customHeight="1">
-      <x:c r="A2" s="27" t="str">
+    <x:row r="2">
+      <x:c r="A2" s="10" t="str">
         <x:v>不变量</x:v>
       </x:c>
-      <x:c r="B2" s="27" t="str">
+      <x:c r="B2" s="10" t="str">
         <x:v>学习资源与阶段</x:v>
       </x:c>
-      <x:c r="C2" s="27" t="str">
+      <x:c r="C2" s="10" t="str">
         <x:v>潜能→灵感转换→固定学习经验满→按实际潜能支付Token→升级</x:v>
       </x:c>
-      <x:c r="D2" s="27" t="str">
+      <x:c r="D2" s="10" t="str">
         <x:v>数值与公式可调；资源身份和阶段顺序不可擅改</x:v>
       </x:c>
-      <x:c r="E2" s="27" t="str">
-        <x:v>固定经验不读取灵感且每级增长；结构修改需用户后续明确确认</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="24" hidden="0" customHeight="1">
-      <x:c r="A3" s="28" t="str">
+      <x:c r="E2" s="10" t="str">
+        <x:v>固定经验不读取灵感、每级增长且始终为偶数；结构修改需用户后续明确确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="10" t="str">
         <x:v>不变量</x:v>
       </x:c>
-      <x:c r="B3" s="28" t="str">
+      <x:c r="B3" s="10" t="str">
         <x:v>战斗输入与职责</x:v>
       </x:c>
-      <x:c r="C3" s="28" t="str">
+      <x:c r="C3" s="10" t="str">
         <x:v>四属性+已装备功法+装备+状态/伤势/精力/加力/主动招式</x:v>
       </x:c>
-      <x:c r="D3" s="28" t="str">
+      <x:c r="D3" s="10" t="str">
         <x:v>玩家与NPC同口径聚合，combatRank仅缩放NPC体力与普通奖励</x:v>
       </x:c>
-      <x:c r="E3" s="28" t="str">
+      <x:c r="E3" s="10" t="str">
         <x:v>不得删除输入、交换四属性职责、让未装备功法生效或加入隐藏倍率</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="28" t="str">
+    <x:row r="4">
+      <x:c r="A4" s="10" t="str">
         <x:v>治理</x:v>
       </x:c>
-      <x:c r="B4" s="28" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>修改授权边界</x:v>
       </x:c>
-      <x:c r="C4" s="28" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>数值、系数、阈值和计算公式可调</x:v>
       </x:c>
-      <x:c r="D4" s="28" t="str">
+      <x:c r="D4" s="10" t="str">
         <x:v>结构修改先列出文件/行为/存档数据/测试影响，再等待一次性确认</x:v>
       </x:c>
-      <x:c r="E4" s="28" t="str">
+      <x:c r="E4" s="10" t="str">
         <x:v>首次提出不视为授权；测试通过不能替代用户确认</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="24" hidden="0" customHeight="1">
-      <x:c r="A5" s="28" t="str">
+    <x:row r="5">
+      <x:c r="A5" s="10" t="str">
         <x:v>目标</x:v>
       </x:c>
-      <x:c r="B5" s="28" t="str">
+      <x:c r="B5" s="10" t="str">
         <x:v>非战斗单位</x:v>
       </x:c>
-      <x:c r="C5" s="28" t="str">
+      <x:c r="C5" s="10" t="str">
         <x:v>均衡新手中位2–4/P90≤5；低编码合法新手中位6–9/P90≤12次攻击尝试</x:v>
       </x:c>
-      <x:c r="D5" s="28" t="str"/>
-      <x:c r="E5" s="28" t="str">
+      <x:c r="D5" s="10" t="str"/>
+      <x:c r="E5" s="10" t="str">
         <x:v>小学生固定100体力，不再被普通攻击一击击倒</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="28" t="str">
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
         <x:v>目标</x:v>
       </x:c>
-      <x:c r="B6" s="28" t="str">
+      <x:c r="B6" s="10" t="str">
         <x:v>同属性同功法镜像战</x:v>
       </x:c>
-      <x:c r="C6" s="28" t="str">
+      <x:c r="C6" s="10" t="str">
         <x:v>8–12 回合</x:v>
       </x:c>
-      <x:c r="D6" s="28" t="str">
+      <x:c r="D6" s="10" t="str">
         <x:v>双方同四维、同功法；无闪避/装备/道具/加力/主动招式；每回合至多各命中一次普攻</x:v>
       </x:c>
-      <x:c r="E6" s="28" t="str">
+      <x:c r="E6" s="10" t="str">
         <x:v>保留暴击、完整功法被动招架、减伤和±10%伤害浮动</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="24" hidden="0" customHeight="1">
-      <x:c r="A7" s="28" t="str">
+    <x:row r="7">
+      <x:c r="A7" s="10" t="str">
         <x:v>校准</x:v>
       </x:c>
-      <x:c r="B7" s="28" t="str">
+      <x:c r="B7" s="10" t="str">
         <x:v>四门派镜像 P10/中位/P90</x:v>
       </x:c>
-      <x:c r="C7" s="28" t="str">
+      <x:c r="C7" s="10" t="str">
         <x:v>L0 8/8/9；L20 8–9/9/10；L60 8–9/9–10/10–11；L100 8–9/9–10/10–11</x:v>
       </x:c>
-      <x:c r="D7" s="28" t="str">
+      <x:c r="D7" s="10" t="str">
         <x:v>NG / React / Vue / Vanilla，各等级10,000次随机模拟</x:v>
       </x:c>
-      <x:c r="E7" s="28" t="str">
+      <x:c r="E7" s="10" t="str">
         <x:v>16组P10、中位与P90全部位于8–12回合</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="28" t="str">
+    <x:row r="8">
+      <x:c r="A8" s="10" t="str">
         <x:v>目标</x:v>
       </x:c>
-      <x:c r="B8" s="28" t="str">
+      <x:c r="B8" s="10" t="str">
         <x:v>精英 / Boss</x:v>
       </x:c>
-      <x:c r="C8" s="28" t="str">
+      <x:c r="C8" s="10" t="str">
         <x:v>8–12 / 10–14 个决策</x:v>
       </x:c>
-      <x:c r="D8" s="28" t="str"/>
-      <x:c r="E8" s="28" t="str">
+      <x:c r="D8" s="10" t="str"/>
+      <x:c r="E8" s="10" t="str">
         <x:v>通过技能与阶段而非无限回血延长</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="28" t="str">
+    <x:row r="9">
+      <x:c r="A9" s="10" t="str">
         <x:v>基础</x:v>
       </x:c>
-      <x:c r="B9" s="28" t="str">
+      <x:c r="B9" s="10" t="str">
         <x:v>攻击</x:v>
       </x:c>
-      <x:c r="C9" s="28" t="str"/>
-      <x:c r="D9" s="28" t="str">
+      <x:c r="C9" s="10" t="str"/>
+      <x:c r="D9" s="10" t="str">
         <x:v>12 + 编码×1.50×centeredScale(编码,0.003,0.94,1.08)</x:v>
       </x:c>
-      <x:c r="E9" s="28" t="str">
+      <x:c r="E9" s="10" t="str">
         <x:v>最少为1，再加功法与装备攻击</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="28" t="str">
+    <x:row r="10">
+      <x:c r="A10" s="10" t="str">
         <x:v>基础</x:v>
       </x:c>
-      <x:c r="B10" s="28" t="str">
+      <x:c r="B10" s="10" t="str">
         <x:v>防御</x:v>
       </x:c>
-      <x:c r="C10" s="28" t="str"/>
-      <x:c r="D10" s="28" t="str">
+      <x:c r="C10" s="10" t="str"/>
+      <x:c r="D10" s="10" t="str">
         <x:v>架构×0.95×centeredScale(架构,0.0025,0.94,1.07)</x:v>
       </x:c>
-      <x:c r="E10" s="28" t="str">
+      <x:c r="E10" s="10" t="str">
         <x:v>最少为0，再加功法与装备防御</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="28" t="str">
+    <x:row r="11">
+      <x:c r="A11" s="10" t="str">
         <x:v>资源</x:v>
       </x:c>
-      <x:c r="B11" s="28" t="str">
+      <x:c r="B11" s="10" t="str">
         <x:v>体力上限</x:v>
       </x:c>
-      <x:c r="C11" s="28" t="str"/>
-      <x:c r="D11" s="28" t="str">
+      <x:c r="C11" s="10" t="str"/>
+      <x:c r="D11" s="10" t="str">
         <x:v>floor(190 + 架构×5.2) + floor(sqrt(精力上限)×3)</x:v>
       </x:c>
-      <x:c r="E11" s="28" t="str">
+      <x:c r="E11" s="10" t="str">
         <x:v>以生命池承载8–12回合基准；精力仍只按平方根反哺体力</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="28" t="str">
+    <x:row r="12">
+      <x:c r="A12" s="10" t="str">
         <x:v>资源</x:v>
       </x:c>
-      <x:c r="B12" s="28" t="str">
+      <x:c r="B12" s="10" t="str">
         <x:v>食物/饮水容量</x:v>
       </x:c>
-      <x:c r="C12" s="28" t="str"/>
-      <x:c r="D12" s="28" t="str">
+      <x:c r="C12" s="10" t="str"/>
+      <x:c r="D12" s="10" t="str">
         <x:v>200 + 编码×6</x:v>
       </x:c>
-      <x:c r="E12" s="28" t="str">
+      <x:c r="E12" s="10" t="str">
         <x:v>创建角色、读档归一化、物品和世界事件共用唯一公式</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="28" t="str">
+    <x:row r="13">
+      <x:c r="A13" s="10" t="str">
         <x:v>资源</x:v>
       </x:c>
-      <x:c r="B13" s="28" t="str">
+      <x:c r="B13" s="10" t="str">
         <x:v>玩家精力上限</x:v>
       </x:c>
-      <x:c r="C13" s="28" t="str"/>
-      <x:c r="D13" s="28" t="str">
+      <x:c r="C13" s="10" t="str"/>
+      <x:c r="D13" s="10" t="str">
         <x:v>精力修为 + 装备功法 mpMaxPerLv 加成</x:v>
       </x:c>
-      <x:c r="E13" s="28" t="str">
+      <x:c r="E13" s="10" t="str">
         <x:v>功法上限字段已接入运行时</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="28" t="str">
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
         <x:v>资源</x:v>
       </x:c>
-      <x:c r="B14" s="28" t="str">
+      <x:c r="B14" s="10" t="str">
         <x:v>NPC精力上限</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="str"/>
-      <x:c r="D14" s="28" t="str">
+      <x:c r="C14" s="10" t="str"/>
+      <x:c r="D14" s="10" t="str">
         <x:v>floor(内功值×25×架构修正) + 装备功法 mpMaxPerLv 加成</x:v>
       </x:c>
-      <x:c r="E14" s="28" t="str">
+      <x:c r="E14" s="10" t="str">
         <x:v>NPC 内功值来自基础架构与已装备门派架构功法</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="28" t="str">
+    <x:row r="15">
+      <x:c r="A15" s="10" t="str">
         <x:v>判定</x:v>
       </x:c>
-      <x:c r="B15" s="28" t="str">
+      <x:c r="B15" s="10" t="str">
         <x:v>命中率</x:v>
       </x:c>
-      <x:c r="C15" s="28" t="str">
+      <x:c r="C15" s="10" t="str">
         <x:v>45%–95%</x:v>
       </x:c>
-      <x:c r="D15" s="28" t="str">
+      <x:c r="D15" s="10" t="str">
         <x:v>clamp(78% + (攻方思维-守方思维)×0.9% + 命中加成 - 闪避加成)</x:v>
       </x:c>
-      <x:c r="E15" s="28" t="str">
+      <x:c r="E15" s="10" t="str">
         <x:v>减少连续空回合</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="28" t="str">
+    <x:row r="16">
+      <x:c r="A16" s="10" t="str">
         <x:v>判定</x:v>
       </x:c>
-      <x:c r="B16" s="28" t="str">
+      <x:c r="B16" s="10" t="str">
         <x:v>减伤率</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="str"/>
-      <x:c r="D16" s="28" t="str">
+      <x:c r="C16" s="10" t="str"/>
+      <x:c r="D16" s="10" t="str">
         <x:v>防御/(防御+100)</x:v>
       </x:c>
-      <x:c r="E16" s="28" t="str">
+      <x:c r="E16" s="10" t="str">
         <x:v>递减收益</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="28" t="str">
+    <x:row r="17">
+      <x:c r="A17" s="10" t="str">
         <x:v>判定</x:v>
       </x:c>
-      <x:c r="B17" s="28" t="str">
+      <x:c r="B17" s="10" t="str">
         <x:v>招架率</x:v>
       </x:c>
-      <x:c r="C17" s="28" t="str">
+      <x:c r="C17" s="10" t="str">
         <x:v>0%–55%</x:v>
       </x:c>
-      <x:c r="D17" s="28" t="str">
+      <x:c r="D17" s="10" t="str">
         <x:v>clamp(4% + 编码×0.25% + 功法/装备招架)</x:v>
       </x:c>
-      <x:c r="E17" s="28" t="str">
+      <x:c r="E17" s="10" t="str">
         <x:v>招架后保留 60% 伤害</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="28" t="str">
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
         <x:v>判定</x:v>
       </x:c>
-      <x:c r="B18" s="28" t="str">
+      <x:c r="B18" s="10" t="str">
         <x:v>暴击率</x:v>
       </x:c>
-      <x:c r="C18" s="28" t="str">
+      <x:c r="C18" s="10" t="str">
         <x:v>2%–30%</x:v>
       </x:c>
-      <x:c r="D18" s="28" t="str">
+      <x:c r="D18" s="10" t="str">
         <x:v>clamp(3% + 灵感×0.30% + 装备暴击)</x:v>
       </x:c>
-      <x:c r="E18" s="28" t="str">
+      <x:c r="E18" s="10" t="str">
         <x:v>暴击属性集中到灵感</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="28" t="str">
+    <x:row r="19">
+      <x:c r="A19" s="10" t="str">
         <x:v>技能</x:v>
       </x:c>
-      <x:c r="B19" s="28" t="str">
+      <x:c r="B19" s="10" t="str">
         <x:v>招式触发</x:v>
       </x:c>
-      <x:c r="C19" s="28" t="str">
+      <x:c r="C19" s="10" t="str">
         <x:v>攻击≤45%；闪避≤27%；招架≤35%</x:v>
       </x:c>
-      <x:c r="D19" s="28" t="str">
+      <x:c r="D19" s="10" t="str">
         <x:v>各类型使用独立 base + count×perMove</x:v>
       </x:c>
-      <x:c r="E19" s="28" t="str">
+      <x:c r="E19" s="10" t="str">
         <x:v>避免多层完全回避锁死战斗</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="28" t="str">
+    <x:row r="20">
+      <x:c r="A20" s="10" t="str">
         <x:v>技能</x:v>
       </x:c>
-      <x:c r="B20" s="28" t="str">
+      <x:c r="B20" s="10" t="str">
         <x:v>加力</x:v>
       </x:c>
-      <x:c r="C20" s="28" t="str">
+      <x:c r="C20" s="10" t="str">
         <x:v>额外伤害≤75%</x:v>
       </x:c>
-      <x:c r="D20" s="28" t="str">
+      <x:c r="D20" s="10" t="str">
         <x:v>伤害×min(75%, 加力/(加力+100))×随机0.9–1.1</x:v>
       </x:c>
-      <x:c r="E20" s="28" t="str">
+      <x:c r="E20" s="10" t="str">
         <x:v>递减收益，不再直接平铺数百点</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="28" t="str">
+    <x:row r="21">
+      <x:c r="A21" s="10" t="str">
         <x:v>AI</x:v>
       </x:c>
-      <x:c r="B21" s="28" t="str">
+      <x:c r="B21" s="10" t="str">
         <x:v>NPC 加力</x:v>
       </x:c>
-      <x:c r="C21" s="28" t="str">
+      <x:c r="C21" s="10" t="str">
         <x:v>默认 45% 概率、25% 内功</x:v>
       </x:c>
-      <x:c r="D21" s="28" t="str">
+      <x:c r="D21" s="10" t="str">
         <x:v>可由 ai.forceUseRate / forceRatio 覆盖</x:v>
       </x:c>
-      <x:c r="E21" s="28" t="str">
+      <x:c r="E21" s="10" t="str">
         <x:v>高阶人物有爆发但不再每击全力</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="28" t="str">
+    <x:row r="22">
+      <x:c r="A22" s="10" t="str">
         <x:v>AI</x:v>
       </x:c>
-      <x:c r="B22" s="28" t="str">
+      <x:c r="B22" s="10" t="str">
         <x:v>NPC 摸鱼</x:v>
       </x:c>
-      <x:c r="C22" s="28" t="str">
+      <x:c r="C22" s="10" t="str">
         <x:v>默认每战 1 次，最多回 18%</x:v>
       </x:c>
-      <x:c r="D22" s="28" t="str">
+      <x:c r="D22" s="10" t="str">
         <x:v>体力低于35%且精力足够时20%概率</x:v>
       </x:c>
-      <x:c r="E22" s="28" t="str">
+      <x:c r="E22" s="10" t="str">
         <x:v>不会反复重置血条</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="28" t="str">
+    <x:row r="23">
+      <x:c r="A23" s="10" t="str">
         <x:v>恢复</x:v>
       </x:c>
-      <x:c r="B23" s="28" t="str">
+      <x:c r="B23" s="10" t="str">
         <x:v>玩家摸鱼 / 用药</x:v>
       </x:c>
-      <x:c r="C23" s="28" t="str">
+      <x:c r="C23" s="10" t="str">
         <x:v>每战 1 次 / 2 次</x:v>
       </x:c>
-      <x:c r="D23" s="28" t="str">
+      <x:c r="D23" s="10" t="str">
         <x:v>摸鱼最多恢复20%最大体力</x:v>
       </x:c>
-      <x:c r="E23" s="28" t="str">
+      <x:c r="E23" s="10" t="str">
         <x:v>受保护 HUD 未改，以次数上限约束免费动作</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="28" t="str">
+    <x:row r="24">
+      <x:c r="A24" s="10" t="str">
         <x:v>伤势</x:v>
       </x:c>
-      <x:c r="B24" s="28" t="str">
+      <x:c r="B24" s="10" t="str">
         <x:v>战后伤势</x:v>
       </x:c>
-      <x:c r="C24" s="28" t="str">
+      <x:c r="C24" s="10" t="str">
         <x:v>单场≤真实体力20%</x:v>
       </x:c>
-      <x:c r="D24" s="28" t="str">
+      <x:c r="D24" s="10" t="str">
         <x:v>净体力损失×15%×(1-功法伤势减免) + 当场重伤</x:v>
       </x:c>
-      <x:c r="E24" s="28" t="str">
+      <x:c r="E24" s="10" t="str">
         <x:v>不按累计受击重复惩罚治疗</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="28" t="str">
+    <x:row r="25">
+      <x:c r="A25" s="10" t="str">
         <x:v>伤势</x:v>
       </x:c>
-      <x:c r="B25" s="28" t="str">
+      <x:c r="B25" s="10" t="str">
         <x:v>破相判定</x:v>
       </x:c>
-      <x:c r="C25" s="28" t="str">
+      <x:c r="C25" s="10" t="str">
         <x:v>濒死15%；归零30%；每次容貌−20</x:v>
       </x:c>
-      <x:c r="D25" s="28" t="str">
+      <x:c r="D25" s="10" t="str">
         <x:v>两项独立判定且可叠加，仅致命战斗触发</x:v>
       </x:c>
-      <x:c r="E25" s="28" t="str">
+      <x:c r="E25" s="10" t="str">
         <x:v>容貌永久损失会写入角色状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="24" hidden="0" customHeight="1">
-      <x:c r="A26" s="28" t="str">
+    <x:row r="26">
+      <x:c r="A26" s="10" t="str">
         <x:v>战败</x:v>
       </x:c>
-      <x:c r="B26" s="28" t="str">
+      <x:c r="B26" s="10" t="str">
         <x:v>资源与功法惩罚</x:v>
       </x:c>
-      <x:c r="C26" s="28" t="str">
+      <x:c r="C26" s="10" t="str">
         <x:v>经验/潜能/Token各−5%～10%；25%概率最多一门功法−1级</x:v>
       </x:c>
-      <x:c r="D26" s="28" t="str">
+      <x:c r="D26" s="10" t="str">
         <x:v>三类资源分别随机5%～10%；仅从高于保底等级的已学功法中随机一门</x:v>
       </x:c>
-      <x:c r="E26" s="28" t="str">
+      <x:c r="E26" s="10" t="str">
         <x:v>结算后立即重算派生属性与体力/精力上限</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="15" hidden="0" customHeight="1">
-      <x:c r="A27" s="28" t="str">
+    <x:row r="27">
+      <x:c r="A27" s="10" t="str">
         <x:v>成长</x:v>
       </x:c>
-      <x:c r="B27" s="28" t="str">
+      <x:c r="B27" s="10" t="str">
         <x:v>固定学习经验</x:v>
       </x:c>
-      <x:c r="C27" s="28" t="str">
-        <x:v>基础Lv1需60；每级至少+20</x:v>
-      </x:c>
-      <x:c r="D27" s="28" t="str">
-        <x:v>10×max(2.25次等级曲线,(5+目标等级)×costFactor,前一级经验单位+2)</x:v>
-      </x:c>
-      <x:c r="E27" s="28" t="str">
-        <x:v>与灵感完全无关；基础前10级为60/80/100/120/140/160/180/200/220/240</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="15" hidden="0" customHeight="1">
-      <x:c r="A28" s="28" t="str">
+      <x:c r="C27" s="10" t="str">
+        <x:v>全功法Lv1需14；此后逐级增加且始终为偶数</x:v>
+      </x:c>
+      <x:c r="D27" s="10" t="str">
+        <x:v>Lv1=14；Lv2+=max(偶数幂曲线,14+偶数化((Lv-1)×2×costFactor),前级+2)</x:v>
+      </x:c>
+      <x:c r="E27" s="10" t="str">
+        <x:v>50灵感时1潜能=14经验；costFactor从Lv2起影响斜率；基础前10级为14/16/18/20/22/24/26/28/30/34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="10" t="str">
         <x:v>成长</x:v>
       </x:c>
-      <x:c r="B28" s="28" t="str">
+      <x:c r="B28" s="10" t="str">
         <x:v>潜能转化学习经验</x:v>
       </x:c>
-      <x:c r="C28" s="28" t="str">
+      <x:c r="C28" s="10" t="str">
         <x:v>灵感0/25/50：每潜能8/10/14经验</x:v>
       </x:c>
-      <x:c r="D28" s="28" t="str">
+      <x:c r="D28" s="10" t="str">
         <x:v>round(10 / clamp(1-(灵感-25)×1.5%,70%,130%))</x:v>
       </x:c>
-      <x:c r="E28" s="28" t="str">
-        <x:v>每个时间片消耗1潜能；灵感越高，升级越快且潜能越省</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="15" hidden="0" customHeight="1">
-      <x:c r="A29" s="28" t="str">
+      <x:c r="E28" s="10" t="str">
+        <x:v>每个时间片消耗1潜能；潜能为0且经验未满时不启动研习或进度条</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="10" t="str">
         <x:v>成长</x:v>
       </x:c>
-      <x:c r="B29" s="28" t="str">
+      <x:c r="B29" s="10" t="str">
         <x:v>师父学习学费</x:v>
       </x:c>
-      <x:c r="C29" s="28" t="str">
+      <x:c r="C29" s="10" t="str">
         <x:v>本级实际潜能消耗的65%</x:v>
       </x:c>
-      <x:c r="D29" s="28" t="str">
+      <x:c r="D29" s="10" t="str">
         <x:v>ceil(本级累计潜能消耗×0.65)</x:v>
       </x:c>
-      <x:c r="E29" s="28" t="str">
+      <x:c r="E29" s="10" t="str">
         <x:v>固定经验满后支付；高灵感因潜能消耗更少而同步节省Token</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="15" hidden="0" customHeight="1">
-      <x:c r="A30" s="28" t="str">
+    <x:row r="30">
+      <x:c r="A30" s="10" t="str">
         <x:v>成长</x:v>
       </x:c>
-      <x:c r="B30" s="28" t="str">
+      <x:c r="B30" s="10" t="str">
         <x:v>标准100级路线</x:v>
       </x:c>
-      <x:c r="C30" s="28" t="str">
-        <x:v>898,040经验 / 89,804潜能 / 58,646 Token</x:v>
-      </x:c>
-      <x:c r="D30" s="28" t="str">
+      <x:c r="C30" s="10" t="str">
+        <x:v>811,616经验 / 81,425潜能 / 53,212 Token</x:v>
+      </x:c>
+      <x:c r="D30" s="10" t="str">
         <x:v>五门基础功法加一门本派架构功法，灵感25</x:v>
       </x:c>
-      <x:c r="E30" s="28" t="str">
-        <x:v>约79.3小时；灵感50为64,401潜能/42,091 Token/约56.9小时</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="15" hidden="0" customHeight="1">
-      <x:c r="A31" s="28" t="str">
+      <x:c r="E30" s="10" t="str">
+        <x:v>约71.9小时；灵感50为58,235潜能/38,136 Token/约51.4小时</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="10" t="str">
+        <x:v>成长</x:v>
+      </x:c>
+      <x:c r="B31" s="10" t="str">
+        <x:v>持续动作频率</x:v>
+      </x:c>
+      <x:c r="C31" s="10" t="str">
+        <x:v>学习10 Hz / 冥想10 Hz / 练功5 Hz</x:v>
+      </x:c>
+      <x:c r="D31" s="10" t="str">
+        <x:v>时间片=1/频率</x:v>
+      </x:c>
+      <x:c r="E31" s="10" t="str">
+        <x:v>学习tick不重复推进全局时钟；冥想与练功按各自时间片推进</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="10" t="str">
+        <x:v>成长</x:v>
+      </x:c>
+      <x:c r="B32" s="10" t="str">
+        <x:v>冥想升级边界</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="str">
+        <x:v>修为+1后当前精力=0</x:v>
+      </x:c>
+      <x:c r="D32" s="10" t="str">
+        <x:v>精力满→清零→修为+1→结束本帧补算→下一tick恢复</x:v>
+      </x:c>
+      <x:c r="E32" s="10" t="str">
+        <x:v>长帧剩余累积留到下一帧，不得跨过0直接显示正数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="10" t="str">
         <x:v>任务</x:v>
       </x:c>
-      <x:c r="B31" s="28" t="str">
+      <x:c r="B33" s="10" t="str">
         <x:v>环任务成长</x:v>
       </x:c>
-      <x:c r="C31" s="28" t="str">
+      <x:c r="C33" s="10" t="str">
         <x:v>线性且封顶</x:v>
       </x:c>
-      <x:c r="D31" s="28" t="str">
+      <x:c r="D33" s="10" t="str">
         <x:v>1 + ringGrowth×(环数-1)，再受 growthCap 限制</x:v>
       </x:c>
-      <x:c r="E31" s="28" t="str">
+      <x:c r="E33" s="10" t="str">
         <x:v>悬赏奖励也改为基于初始值线性成长</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="15" hidden="0" customHeight="1">
-      <x:c r="A32" s="28" t="str">
+    <x:row r="34">
+      <x:c r="A34" s="10" t="str">
         <x:v>任务</x:v>
       </x:c>
-      <x:c r="B32" s="28" t="str">
+      <x:c r="B34" s="10" t="str">
         <x:v>奖励互斥</x:v>
       </x:c>
-      <x:c r="C32" s="28" t="str">
+      <x:c r="C34" s="10" t="str">
         <x:v>任务奖励或野战奖励二选一</x:v>
       </x:c>
-      <x:c r="D32" s="28" t="str">
+      <x:c r="D34" s="10" t="str">
         <x:v>普通悬赏击杀先标记完成，回程交付时才发奖</x:v>
       </x:c>
-      <x:c r="E32" s="28" t="str">
+      <x:c r="E34" s="10" t="str">
         <x:v>防止同一目标重复获得两份奖励</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="15" hidden="0" customHeight="1">
-      <x:c r="A33" s="28" t="str">
+    <x:row r="35">
+      <x:c r="A35" s="10" t="str">
         <x:v>任务</x:v>
       </x:c>
-      <x:c r="B33" s="28" t="str">
+      <x:c r="B35" s="10" t="str">
         <x:v>交付物退款</x:v>
       </x:c>
-      <x:c r="C33" s="28" t="str">
+      <x:c r="C35" s="10" t="str">
         <x:v>固定成本补偿</x:v>
       </x:c>
-      <x:c r="D33" s="28" t="str">
+      <x:c r="D35" s="10" t="str">
         <x:v>物品价格×itemRefundRate</x:v>
       </x:c>
-      <x:c r="E33" s="28" t="str">
+      <x:c r="E35" s="10" t="str">
         <x:v>退款不参与环数成长或随机浮动，服务费才属于奖励</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="15" hidden="0" customHeight="1">
-      <x:c r="A34" s="29" t="str">
+    <x:row r="36">
+      <x:c r="A36" s="10" t="str">
         <x:v>任务</x:v>
       </x:c>
-      <x:c r="B34" s="29" t="str">
+      <x:c r="B36" s="10" t="str">
         <x:v>导师新手项目</x:v>
       </x:c>
-      <x:c r="C34" s="29" t="str">
+      <x:c r="C36" s="10" t="str">
         <x:v>50经验 / 50潜能 / 40 Token</x:v>
       </x:c>
-      <x:c r="D34" s="29" t="str">
+      <x:c r="D36" s="10" t="str">
         <x:v>三个项目奖励固定，仅体力消耗分别为25/50/100</x:v>
       </x:c>
-      <x:c r="E34" s="29" t="str">
+      <x:c r="E36" s="10" t="str">
         <x:v>项目难度不再放大奖励</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="15" hidden="0" customHeight="1">
-      <x:c r="A35" s="30" t="str">
+    <x:row r="37">
+      <x:c r="A37" s="10" t="str">
         <x:v>任务</x:v>
       </x:c>
-      <x:c r="B35" s="30" t="str">
+      <x:c r="B37" s="10" t="str">
         <x:v>并行任务状态</x:v>
       </x:c>
-      <x:c r="C35" s="30" t="str">
+      <x:c r="C37" s="10" t="str">
         <x:v>不同任务可同时活动</x:v>
       </x:c>
-      <x:c r="D35" s="30" t="str">
+      <x:c r="D37" s="10" t="str">
         <x:v>固定任务按 quest_id；生成任务按 generator:&lt;generator_id&gt; 唯一</x:v>
       </x:c>
-      <x:c r="E35" s="30" t="str">
+      <x:c r="E37" s="10" t="str">
         <x:v>同一 runtime_id/生成器不可重复；任务仅存本局内存，重开或读档时清空</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="28.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A36" s="30" t="str">
+    <x:row r="38">
+      <x:c r="A38" s="10" t="str">
         <x:v>任务</x:v>
       </x:c>
-      <x:c r="B36" s="30" t="str">
+      <x:c r="B38" s="10" t="str">
         <x:v>随机目标过滤</x:v>
       </x:c>
-      <x:c r="C36" s="30" t="str">
+      <x:c r="C38" s="10" t="str">
         <x:v>保护任务端点、非战斗与剧情人物</x:v>
       </x:c>
-      <x:c r="D36" s="30" t="str">
+      <x:c r="D38" s="10" t="str">
         <x:v>排除全部任务发布/交付端点、当前目标；击杀池另排除未满18岁、noncombatant、商贩、典当商、师父、显式保护人物</x:v>
       </x:c>
-      <x:c r="E36" s="30" t="str">
+      <x:c r="E38" s="10" t="str">
         <x:v>只有悬赏/击杀环响应击败事件，跑腿与谈话任务必须交付</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="15" hidden="0" customHeight="1">
-      <x:c r="A37" s="30" t="str">
+    <x:row r="39">
+      <x:c r="A39" s="10" t="str">
         <x:v>人物</x:v>
       </x:c>
-      <x:c r="B37" s="30" t="str">
+      <x:c r="B39" s="10" t="str">
         <x:v>combatRank</x:v>
       </x:c>
-      <x:c r="C37" s="30" t="str">
+      <x:c r="C39" s="10" t="str">
         <x:v>noncombatant→legendary 共7档</x:v>
       </x:c>
-      <x:c r="D37" s="30" t="str">
+      <x:c r="D39" s="10" t="str">
         <x:v>仅缩放生命池与普通奖励</x:v>
       </x:c>
-      <x:c r="E37" s="30" t="str">
+      <x:c r="E39" s="10" t="str">
         <x:v>攻击、防御仍来自显式四维、功法、装备</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="15" hidden="0" customHeight="1">
-      <x:c r="A38" s="30" t="str">
+    <x:row r="40">
+      <x:c r="A40" s="10" t="str">
         <x:v>人物</x:v>
       </x:c>
-      <x:c r="B38" s="30" t="str">
+      <x:c r="B40" s="10" t="str">
         <x:v>combatRank 生命倍率</x:v>
       </x:c>
-      <x:c r="C38" s="30" t="str">
+      <x:c r="C40" s="10" t="str">
         <x:v>0.50 / 0.78 / 0.92 / 1.00 / 1.10 / 1.20 / 1.30</x:v>
       </x:c>
-      <x:c r="D38" s="30" t="str">
+      <x:c r="D40" s="10" t="str">
         <x:v>noncombatant / novice / trained / veteran / elite / master / legendary</x:v>
       </x:c>
-      <x:c r="E38" s="30" t="str">
+      <x:c r="E40" s="10" t="str">
         <x:v>小学生为noncombatant：1.8架构、0精力时最终100体力</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="15" hidden="0" customHeight="1">
-      <x:c r="A39" s="30" t="str">
+    <x:row r="41">
+      <x:c r="A41" s="10" t="str">
         <x:v>人物</x:v>
       </x:c>
-      <x:c r="B39" s="30" t="str">
+      <x:c r="B41" s="10" t="str">
         <x:v>combatRank 奖励倍率</x:v>
       </x:c>
-      <x:c r="C39" s="30" t="str">
+      <x:c r="C41" s="10" t="str">
         <x:v>0.15 / 0.50 / 0.75 / 1.00 / 1.20 / 1.50 / 2.00</x:v>
       </x:c>
-      <x:c r="D39" s="30" t="str">
+      <x:c r="D41" s="10" t="str">
         <x:v>noncombatant / novice / trained / veteran / elite / master / legendary</x:v>
       </x:c>
-      <x:c r="E39" s="30" t="str">
+      <x:c r="E41" s="10" t="str">
         <x:v>战斗奖励与生命倍率分离，非战斗人物不成为刷取目标</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="15" hidden="0" customHeight="1">
-      <x:c r="A40" s="30" t="str">
+    <x:row r="42">
+      <x:c r="A42" s="10" t="str">
         <x:v>人物</x:v>
       </x:c>
-      <x:c r="B40" s="30" t="str">
+      <x:c r="B42" s="10" t="str">
         <x:v>combatRole</x:v>
       </x:c>
-      <x:c r="C40" s="30" t="str">
+      <x:c r="C42" s="10" t="str">
         <x:v>7种原型</x:v>
       </x:c>
-      <x:c r="D40" s="30" t="str">
+      <x:c r="D42" s="10" t="str">
         <x:v>noncombatant/striker/skirmisher/tank/counter/controller/balanced</x:v>
       </x:c>
-      <x:c r="E40" s="30" t="str">
+      <x:c r="E42" s="10" t="str">
         <x:v>66 人四维配点全部唯一且总点数不变</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="15" hidden="0" customHeight="1">
-      <x:c r="A41" s="30" t="str">
+    <x:row r="43">
+      <x:c r="A43" s="10" t="str">
         <x:v>状态</x:v>
       </x:c>
-      <x:c r="B41" s="30" t="str">
+      <x:c r="B43" s="10" t="str">
         <x:v>资源归一化</x:v>
       </x:c>
-      <x:c r="C41" s="30" t="str">
+      <x:c r="C43" s="10" t="str">
         <x:v>上限变化即时钳制</x:v>
       </x:c>
-      <x:c r="D41" s="30" t="str">
+      <x:c r="D43" s="10" t="str">
         <x:v>卸功法或战败降级后重算四维、体力与精力上限</x:v>
       </x:c>
-      <x:c r="E41" s="30" t="str">
+      <x:c r="E43" s="10" t="str">
         <x:v>不允许保存当前值高于新上限</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="15" hidden="0" customHeight="1">
-      <x:c r="A42" s="30" t="str">
+    <x:row r="44">
+      <x:c r="A44" s="10" t="str">
         <x:v>界面</x:v>
       </x:c>
-      <x:c r="B42" s="30" t="str">
+      <x:c r="B44" s="10" t="str">
         <x:v>战斗大数值排版</x:v>
       </x:c>
-      <x:c r="C42" s="30" t="str">
+      <x:c r="C44" s="10" t="str">
         <x:v>体力与精力支持5–6位数</x:v>
       </x:c>
-      <x:c r="D42" s="30" t="str">
+      <x:c r="D44" s="10" t="str">
         <x:v>双方统计分列显示；伤势百分比独立位于体力条上方</x:v>
       </x:c>
-      <x:c r="E42" s="30" t="str">
+      <x:c r="E44" s="10" t="str">
         <x:v>数值、标签和进度条不得互相覆盖</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="15" hidden="0" customHeight="1">
-      <x:c r="A43" s="30" t="str">
+    <x:row r="45">
+      <x:c r="A45" s="10" t="str">
         <x:v>界面</x:v>
       </x:c>
-      <x:c r="B43" s="30" t="str">
+      <x:c r="B45" s="10" t="str">
         <x:v>顶部进度条宽度</x:v>
       </x:c>
-      <x:c r="C43" s="30" t="str">
+      <x:c r="C45" s="10" t="str">
         <x:v>从地图徽标后8px延伸至右边界前16px</x:v>
       </x:c>
-      <x:c r="D43" s="30" t="str">
+      <x:c r="D45" s="10" t="str">
         <x:v>left=mapBadge.right+8；right=viewportWidth-16</x:v>
       </x:c>
-      <x:c r="E43" s="30" t="str">
+      <x:c r="E45" s="10" t="str">
         <x:v>480逻辑视口下约316px，充分使用右侧空间</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="15" hidden="0" customHeight="1">
-      <x:c r="A44" s="30" t="str">
+    <x:row r="46">
+      <x:c r="A46" s="10" t="str">
         <x:v>存档</x:v>
       </x:c>
-      <x:c r="B44" s="30" t="str">
+      <x:c r="B46" s="10" t="str">
         <x:v>v5 版本边界</x:v>
       </x:c>
-      <x:c r="C44" s="30" t="str">
+      <x:c r="C46" s="10" t="str">
         <x:v>仅接受当前版本</x:v>
       </x:c>
-      <x:c r="D44" s="30" t="str">
+      <x:c r="D46" s="10" t="str">
         <x:v>version == 5</x:v>
       </x:c>
-      <x:c r="E44" s="30" t="str">
+      <x:c r="E46" s="10" t="str">
         <x:v>资源主键已切换为 UUID；v2、v3、v4 存档全部作废且不迁移</x:v>
       </x:c>
     </x:row>

--- a/docs/data/balance-rules.xlsx
+++ b/docs/data/balance-rules.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R037e527f8efe4354"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRules" sheetId="2" r:id="R9324cf74bdf64481"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R324ce0afd968496e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRules" sheetId="2" r:id="R89156b32e673479f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1183,6 +1183,91 @@
         <x:v>资源主键已切换为 UUID；v2、v3、v4 存档全部作废且不迁移</x:v>
       </x:c>
     </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>技能</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>绝招成长硬锁</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>仅接受当前门派、装备与等级解锁列表中的标准绝招 ID</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>门派架构30级解锁一档，80级解锁二档；执行前按ID重新解析权威配置</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>外部字典不能伪造能力、精力消耗或等级绕过门槛</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>技能</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>绝招两档平衡</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>一档效果等级最多74；二档使用完整功力</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>effect_level = min(innerLevel,74)（一档）/ innerLevel（二档）</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>80级后形成低耗稳定与高耗完整的选择，不再是同效果不同价格</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>AI</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>角色化意图决策</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>striker偏加力；controller偏绝招；tank偏恢复；其余原型各有概率曲线</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>combatRole默认行为可由ai.ultUseRate/forceUseRate/restUseRate/itemUseRate覆盖</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>下一回合意图先写入【预判】战报；原型不直接修改攻防命中或伤害</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>人物</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>NPC击败后果</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>静态NPC冷却300游戏秒，累计落败次数随v5角色存档保持</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>defeated_until + defeat_counts；动态任务NPC仍只保留本局状态</x:v>
+      </x:c>
+      <x:c r="E50" t="str">
+        <x:v>胜利立即安全保存；复出后对白与人物详情反馈历史交手</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>发布</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>发布前闸门</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>数据/预设/文件规模/Godot全量测试全部通过</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>npm run release:check</x:v>
+      </x:c>
+      <x:c r="E51" t="str">
+        <x:v>测试先完整--import，使用/tmp日志与存档，逐例90秒超时并扫描脚本加载错误</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
